--- a/data/rr_table_step.xlsx
+++ b/data/rr_table_step.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315E9393-7B75-E44B-993C-F996D33B3F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3577AD-4F49-984B-A8C7-F648DF950C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31220" yWindow="300" windowWidth="28800" windowHeight="16100" activeTab="2" xr2:uid="{8D5AF9D6-033C-0248-AC54-73E73626E3DE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" activeTab="2" xr2:uid="{8D5AF9D6-033C-0248-AC54-73E73626E3DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
@@ -504,17 +504,10 @@
       <c r="C3">
         <v>0.99054730264050606</v>
       </c>
-      <c r="D3" s="1">
-        <v>1.0002312179999999</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.98734633000000005</v>
-      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
       <c r="F3">
         <v>0.98767208497389603</v>
-      </c>
-      <c r="G3">
-        <v>0.99029234399999999</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -527,17 +520,10 @@
       <c r="C4">
         <v>0.86999592142207705</v>
       </c>
-      <c r="D4" s="1">
-        <v>0.97519536299999998</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.93292032999999996</v>
-      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
       <c r="F4">
         <v>0.802692892265081</v>
-      </c>
-      <c r="G4">
-        <v>0.89691209999999999</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -550,17 +536,10 @@
       <c r="C5">
         <v>0.78092097761533597</v>
       </c>
-      <c r="D5" s="1">
-        <v>0.95077829700000005</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.87765811000000005</v>
-      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
       <c r="F5">
         <v>0.66422872369433394</v>
-      </c>
-      <c r="G5">
-        <v>0.81636997</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -573,17 +552,10 @@
       <c r="C6">
         <v>0.72578417029272801</v>
       </c>
-      <c r="D6" s="1">
-        <v>0.92698025100000003</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.82566938999999995</v>
-      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
       <c r="F6">
         <v>0.57759413920027103</v>
-      </c>
-      <c r="G6">
-        <v>0.73210290200000006</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -596,17 +568,10 @@
       <c r="C7">
         <v>0.69842658049740303</v>
       </c>
-      <c r="D7" s="1">
-        <v>0.90377040099999995</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.77676025999999998</v>
-      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
       <c r="F7">
         <v>0.54717719375149798</v>
-      </c>
-      <c r="G7">
-        <v>0.66636053299999998</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -698,18 +663,11 @@
       <c r="C3">
         <v>0.99054730264050606</v>
       </c>
-      <c r="D3">
-        <v>1.0002312183081601</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.98734633000000005</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3">
         <v>0.98767208497389603</v>
       </c>
-      <c r="G3" s="1">
-        <v>0.99029234399999999</v>
-      </c>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -721,18 +679,11 @@
       <c r="C4">
         <v>0.81150553569056405</v>
       </c>
-      <c r="D4">
-        <v>0.94973339637425103</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.87765811000000005</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4">
         <v>0.74683219337600304</v>
       </c>
-      <c r="G4" s="1">
-        <v>0.87497672000000004</v>
-      </c>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -744,18 +695,11 @@
       <c r="C5">
         <v>0.70045362354503704</v>
       </c>
-      <c r="D5">
-        <v>0.89780999806166695</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.78015559000000001</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5">
         <v>0.58020394448714896</v>
       </c>
-      <c r="G5" s="1">
-        <v>0.77692706700000003</v>
-      </c>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -767,18 +711,11 @@
       <c r="C6">
         <v>0.636992396229353</v>
       </c>
-      <c r="D6">
-        <v>0.85248302907414297</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.68746187999999997</v>
-      </c>
+      <c r="E6" s="1"/>
       <c r="F6">
         <v>0.48446756912310301</v>
       </c>
-      <c r="G6" s="1">
-        <v>0.68306597300000005</v>
-      </c>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -790,18 +727,11 @@
       <c r="C7">
         <v>0.61565388415823796</v>
       </c>
-      <c r="D7">
-        <v>0.80943775199485601</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.60842947999999997</v>
-      </c>
+      <c r="E7" s="1"/>
       <c r="F7">
         <v>0.45483525662899998</v>
       </c>
-      <c r="G7" s="1">
-        <v>0.60054430199999997</v>
-      </c>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -892,17 +822,9 @@
       <c r="C3" s="1">
         <v>0.99054730300000005</v>
       </c>
-      <c r="D3" s="2">
-        <v>1.0002312200000001</v>
-      </c>
-      <c r="E3">
-        <v>0.98734633487204804</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="F3">
         <v>0.98767208497389603</v>
-      </c>
-      <c r="G3">
-        <v>0.99029234399999999</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -915,17 +837,9 @@
       <c r="C4" s="1">
         <v>0.92462308100000001</v>
       </c>
-      <c r="D4" s="2">
-        <v>0.99477459000000001</v>
-      </c>
-      <c r="E4">
-        <v>0.99166216992258405</v>
-      </c>
+      <c r="D4" s="2"/>
       <c r="F4">
         <v>0.86273179572012704</v>
-      </c>
-      <c r="G4">
-        <v>0.92396164700000005</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -938,17 +852,9 @@
       <c r="C5" s="1">
         <v>0.86685345400000002</v>
       </c>
-      <c r="D5" s="2">
-        <v>0.99810295999999998</v>
-      </c>
-      <c r="E5">
-        <v>0.99166216992258405</v>
-      </c>
+      <c r="D5" s="2"/>
       <c r="F5">
         <v>0.75700147923349603</v>
-      </c>
-      <c r="G5">
-        <v>0.86207384200000003</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -961,17 +867,9 @@
       <c r="C6" s="1">
         <v>0.82336353100000004</v>
       </c>
-      <c r="D6" s="2">
-        <v>1.003625</v>
-      </c>
-      <c r="E6">
-        <v>0.98734633487204804</v>
-      </c>
+      <c r="D6" s="2"/>
       <c r="F6">
         <v>0.6886219241514</v>
-      </c>
-      <c r="G6">
-        <v>0.80035804200000005</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -984,17 +882,9 @@
       <c r="C7" s="1">
         <v>0.792327801</v>
       </c>
-      <c r="D7" s="2">
-        <v>1.0003806200000001</v>
-      </c>
-      <c r="E7">
-        <v>0.98734633487204804</v>
-      </c>
+      <c r="D7" s="2"/>
       <c r="F7">
         <v>0.65826665149219399</v>
-      </c>
-      <c r="G7">
-        <v>0.74306047200000003</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
